--- a/template.xlsx
+++ b/template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khang\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Khang\Documents\Github\Debt-Calculation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B782668E-99E1-43E9-B8BC-27300E35AE2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF2B4781-20CD-4440-9BC0-37C9908DDBB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t>Cửa hàng</t>
   </si>
@@ -115,16 +115,32 @@
   </si>
   <si>
     <t>755 Nguyễn Văn Linh, ấp Năm Trại, Hòa Thành Tây Ninh – Số điện thoại: 0947381573, 0984012265</t>
+  </si>
+  <si>
+    <t>Ngày</t>
+  </si>
+  <si>
+    <t>Tên sản phẩm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Số lượng </t>
+  </si>
+  <si>
+    <t>Đơn giá</t>
+  </si>
+  <si>
+    <t>Tổng hóa đơn</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd/mm/yy"/>
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0\ [$₫-42A]_-;\-* #,##0\ [$₫-42A]_-;_-* &quot;-&quot;\ [$₫-42A]_-;_-@_-"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -201,6 +217,41 @@
     <font>
       <i/>
       <sz val="8"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="1"/>
@@ -214,30 +265,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -263,50 +296,6 @@
         <color auto="1"/>
       </left>
       <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right/>
       <top style="medium">
         <color auto="1"/>
       </top>
@@ -333,11 +322,43 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
@@ -349,39 +370,17 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -391,7 +390,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -400,88 +399,136 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -610,39 +657,39 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19" style="33" customWidth="1"/>
+    <col min="1" max="1" width="19" style="23" customWidth="1"/>
     <col min="2" max="4" width="19" style="3" customWidth="1"/>
-    <col min="5" max="5" width="19" style="19" customWidth="1"/>
+    <col min="5" max="5" width="19" style="9" customWidth="1"/>
     <col min="6" max="6" width="16" style="2" customWidth="1"/>
     <col min="7" max="7" width="13.85546875" style="2" customWidth="1"/>
     <col min="12" max="16384" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="59"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="34"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="4" customFormat="1" ht="41.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="21"/>
-      <c r="B3" s="22"/>
-      <c r="C3" s="23" t="s">
+      <c r="A3" s="11"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="24"/>
-      <c r="E3" s="19"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="9"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
@@ -651,20 +698,17 @@
       <c r="K3" s="2"/>
     </row>
     <row r="4" spans="1:11" s="5" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="24"/>
-      <c r="D4" s="27" t="s">
+      <c r="C4" s="14"/>
+      <c r="D4" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="28">
-        <f ca="1">TODAY()</f>
-        <v>45766</v>
-      </c>
+      <c r="E4" s="18"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
@@ -673,17 +717,17 @@
       <c r="K4" s="2"/>
     </row>
     <row r="5" spans="1:11" s="5" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="24"/>
-      <c r="D5" s="27" t="s">
+      <c r="C5" s="14"/>
+      <c r="D5" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="29"/>
+      <c r="E5" s="19"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -692,15 +736,15 @@
       <c r="K5" s="2"/>
     </row>
     <row r="6" spans="1:11" s="5" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="24"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="29"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="19"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -709,17 +753,17 @@
       <c r="K6" s="2"/>
     </row>
     <row r="7" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="24"/>
-      <c r="D7" s="27" t="s">
+      <c r="C7" s="14"/>
+      <c r="D7" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="32" t="s">
+      <c r="E7" s="22" t="s">
         <v>14</v>
       </c>
       <c r="H7" s="2"/>
@@ -727,85 +771,85 @@
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D8" s="6"/>
     </row>
-    <row r="9" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="34" t="s">
+    <row r="9" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="35"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="34"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" s="36"/>
-      <c r="B10" s="24"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="29"/>
-    </row>
-    <row r="11" spans="1:11" s="5" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A11" s="37"/>
-      <c r="B11" s="38" t="s">
+      <c r="A10" s="24"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="19"/>
+    </row>
+    <row r="11" spans="1:11" s="66" customFormat="1" ht="27" x14ac:dyDescent="0.25">
+      <c r="A11" s="61"/>
+      <c r="B11" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="63" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="38" t="s">
+      <c r="D11" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="40" t="s">
+      <c r="E11" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
+      <c r="F11" s="65"/>
+      <c r="G11" s="65"/>
+      <c r="H11" s="65"/>
+      <c r="I11" s="65"/>
+      <c r="J11" s="65"/>
+      <c r="K11" s="65"/>
     </row>
     <row r="12" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="41"/>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="43"/>
+      <c r="A12" s="26"/>
+      <c r="B12" s="35"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="37"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
     </row>
     <row r="13" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="41"/>
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="43"/>
+      <c r="A13" s="26"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="37"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
     </row>
     <row r="14" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="41"/>
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="43"/>
+      <c r="A14" s="26"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="37"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
     </row>
-    <row r="15" spans="1:11" ht="15" x14ac:dyDescent="0.2">
-      <c r="A15" s="44"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="43"/>
+    <row r="15" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="28"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="37"/>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="2"/>
@@ -813,29 +857,37 @@
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
     </row>
-    <row r="16" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="34" t="s">
+    <row r="16" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="35"/>
-    </row>
-    <row r="17" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="45"/>
-      <c r="D17" s="46"/>
-      <c r="E17" s="47"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-    </row>
-    <row r="18" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D18" s="46"/>
-      <c r="E18" s="47"/>
+      <c r="B16" s="33"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="34"/>
+    </row>
+    <row r="17" spans="1:11" s="41" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="39" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="40" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="42" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" s="29"/>
+      <c r="C18" s="67"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="69"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
@@ -843,9 +895,11 @@
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
     </row>
-    <row r="19" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D19" s="46"/>
-      <c r="E19" s="47"/>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A19" s="29"/>
+      <c r="C19" s="67"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="69"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
@@ -853,10 +907,11 @@
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
     </row>
-    <row r="20" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C20" s="6"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="47"/>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20" s="29"/>
+      <c r="C20" s="67"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="69"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
@@ -864,7 +919,11 @@
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
     </row>
-    <row r="21" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A21" s="29"/>
+      <c r="C21" s="67"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="69"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
@@ -872,66 +931,98 @@
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
     </row>
-    <row r="22" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="48"/>
-      <c r="B22" s="9" t="s">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C22" s="67"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="69"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C23" s="68"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="69"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+    </row>
+    <row r="24" spans="1:11" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C24" s="67"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+    </row>
+    <row r="25" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="44"/>
+      <c r="B25" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="10"/>
-      <c r="D22" s="9" t="s">
+      <c r="C25" s="46"/>
+      <c r="D25" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="E22" s="49"/>
-    </row>
-    <row r="23" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="50" t="s">
+      <c r="E25" s="47"/>
+    </row>
+    <row r="26" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="22"/>
-      <c r="D23" s="50" t="s">
+      <c r="C26" s="12"/>
+      <c r="D26" s="31" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="1:11" s="12" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="51"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="52"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-    </row>
-    <row r="29" spans="1:11" s="12" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="53"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="14" t="s">
+    <row r="31" spans="1:11" s="8" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="58"/>
+      <c r="B31" s="59"/>
+      <c r="C31" s="59"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="60"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+    </row>
+    <row r="32" spans="1:11" s="8" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="48"/>
+      <c r="B32" s="49"/>
+      <c r="C32" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="15"/>
-      <c r="E29" s="54"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-    </row>
-    <row r="30" spans="1:11" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="55"/>
-      <c r="B30" s="16"/>
-      <c r="C30" s="17" t="s">
+      <c r="D32" s="51"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+    </row>
+    <row r="33" spans="1:11" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="53"/>
+      <c r="B33" s="54"/>
+      <c r="C33" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="D30" s="18"/>
-      <c r="E30" s="56"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
+      <c r="D33" s="56"/>
+      <c r="E33" s="57"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="0.78749999999999998" bottom="0.95416666666666705" header="0.511811023622047" footer="0.78749999999999998"/>

--- a/template.xlsx
+++ b/template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Khang\Documents\Github\Debt-Calculation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF2B4781-20CD-4440-9BC0-37C9908DDBB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA64A381-7BFA-422D-BF98-A23386DAD4C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,13 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
-  <si>
-    <t>Cửa hàng</t>
-  </si>
-  <si>
-    <t>Vật Tư Nông Nghiệp Nam Khang</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
   <si>
     <t>BÁO CÁO THANH TOÁN CÔNG NỢ</t>
   </si>
@@ -114,22 +108,16 @@
     <t>CỬA HÀNG VẬT TƯ NÔNG NGHIỆP NAM KHANG</t>
   </si>
   <si>
-    <t>755 Nguyễn Văn Linh, ấp Năm Trại, Hòa Thành Tây Ninh – Số điện thoại: 0947381573, 0984012265</t>
-  </si>
-  <si>
-    <t>Ngày</t>
-  </si>
-  <si>
-    <t>Tên sản phẩm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Số lượng </t>
-  </si>
-  <si>
-    <t>Đơn giá</t>
-  </si>
-  <si>
-    <t>Tổng hóa đơn</t>
+    <t>CỬA HÀNG</t>
+  </si>
+  <si>
+    <t>VẬT TƯ NÔNG NGHIỆP NAM KHANG</t>
+  </si>
+  <si>
+    <t>Hóa đơn ngày</t>
+  </si>
+  <si>
+    <t>Địa chỉ: 755 Nguyễn Văn Linh, ấp Năm Trại, Hòa Thành Tây Ninh – Số điện thoại: 0947381573, 0984012265.</t>
   </si>
 </sst>
 </file>
@@ -140,7 +128,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0\ [$₫-42A]_-;\-* #,##0\ [$₫-42A]_-;_-* &quot;-&quot;\ [$₫-42A]_-;_-@_-"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -154,22 +142,8 @@
       <charset val="1"/>
     </font>
     <font>
-      <i/>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <b/>
       <sz val="12"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="1"/>
@@ -235,14 +209,6 @@
       <family val="1"/>
     </font>
     <font>
-      <b/>
-      <i/>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <i/>
       <sz val="10"/>
       <name val="Arial"/>
@@ -251,6 +217,35 @@
     </font>
     <font>
       <i/>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="18"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -265,7 +260,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -353,12 +348,43 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="dotted">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="dotted">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="dotted">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
@@ -369,8 +395,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -379,62 +405,48 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -443,30 +455,16 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
     </xf>
@@ -477,9 +475,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1"/>
@@ -492,7 +487,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1"/>
@@ -504,27 +499,87 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -657,10 +712,10 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19" style="23" customWidth="1"/>
+    <col min="1" max="1" width="19" style="21" customWidth="1"/>
     <col min="2" max="4" width="19" style="3" customWidth="1"/>
     <col min="5" max="5" width="19" style="9" customWidth="1"/>
     <col min="6" max="6" width="16" style="2" customWidth="1"/>
@@ -669,26 +724,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="28"/>
+    </row>
+    <row r="2" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="59" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="4" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="10"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="34"/>
-    </row>
-    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" s="4" customFormat="1" ht="41.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="11"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="14"/>
+      <c r="D3" s="12"/>
       <c r="E3" s="9"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -698,17 +753,17 @@
       <c r="K3" s="2"/>
     </row>
     <row r="4" spans="1:11" s="5" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="12"/>
+      <c r="D4" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="18"/>
+      <c r="E4" s="16"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
@@ -717,17 +772,17 @@
       <c r="K4" s="2"/>
     </row>
     <row r="5" spans="1:11" s="5" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="12"/>
+      <c r="D5" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="19"/>
+      <c r="E5" s="17"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -736,15 +791,15 @@
       <c r="K5" s="2"/>
     </row>
     <row r="6" spans="1:11" s="5" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="19"/>
+      <c r="A6" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="12"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="17"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -753,18 +808,18 @@
       <c r="K6" s="2"/>
     </row>
     <row r="7" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="12"/>
+      <c r="D7" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="E7" s="20" t="s">
         <v>12</v>
-      </c>
-      <c r="C7" s="14"/>
-      <c r="D7" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>14</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
@@ -775,81 +830,83 @@
       <c r="D8" s="6"/>
     </row>
     <row r="9" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="43" t="s">
+      <c r="A9" s="74" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="28"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" s="22"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="17"/>
+    </row>
+    <row r="11" spans="1:11" s="49" customFormat="1" ht="27" x14ac:dyDescent="0.25">
+      <c r="A11" s="60" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="61" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="33"/>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="34"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" s="24"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="19"/>
-    </row>
-    <row r="11" spans="1:11" s="66" customFormat="1" ht="27" x14ac:dyDescent="0.25">
-      <c r="A11" s="61"/>
-      <c r="B11" s="62" t="s">
+      <c r="D11" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="63" t="s">
+      <c r="E11" s="63" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="62" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" s="64" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" s="65"/>
-      <c r="G11" s="65"/>
-      <c r="H11" s="65"/>
-      <c r="I11" s="65"/>
-      <c r="J11" s="65"/>
-      <c r="K11" s="65"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="48"/>
+      <c r="K11" s="48"/>
     </row>
     <row r="12" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="26"/>
-      <c r="B12" s="35"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="37"/>
+      <c r="A12" s="70"/>
+      <c r="B12" s="71"/>
+      <c r="C12" s="72"/>
+      <c r="D12" s="71"/>
+      <c r="E12" s="73"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
     </row>
     <row r="13" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="26"/>
-      <c r="B13" s="35"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="37"/>
+      <c r="A13" s="23"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="31"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
     </row>
     <row r="14" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="26"/>
-      <c r="B14" s="35"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="37"/>
+      <c r="A14" s="23"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="31"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
     </row>
     <row r="15" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="28"/>
-      <c r="B15" s="36"/>
+      <c r="A15" s="25"/>
+      <c r="B15" s="30"/>
       <c r="C15" s="7"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="37"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="31"/>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="2"/>
@@ -858,48 +915,34 @@
       <c r="K15" s="2"/>
     </row>
     <row r="16" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="43" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="33"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="34"/>
-    </row>
-    <row r="17" spans="1:11" s="41" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="40" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" s="42" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" s="29"/>
-      <c r="C18" s="67"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="69"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A19" s="29"/>
-      <c r="C19" s="67"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="69"/>
+      <c r="A16" s="74" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="28"/>
+    </row>
+    <row r="17" spans="1:11" s="32" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="66"/>
+      <c r="B17" s="67"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="69"/>
+    </row>
+    <row r="18" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="65"/>
+      <c r="B18" s="51"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="54"/>
+    </row>
+    <row r="19" spans="1:11" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="56"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="55"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
@@ -907,122 +950,66 @@
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" s="29"/>
-      <c r="C20" s="67"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="69"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A21" s="29"/>
-      <c r="C21" s="67"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="69"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="C22" s="67"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="69"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="C23" s="68"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="69"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-    </row>
-    <row r="24" spans="1:11" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C24" s="67"/>
-      <c r="E24" s="70"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-    </row>
-    <row r="25" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="44"/>
-      <c r="B25" s="45" t="s">
+    <row r="20" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="33"/>
+      <c r="B20" s="75" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="34"/>
+      <c r="D20" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="35"/>
+    </row>
+    <row r="21" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="C25" s="46"/>
-      <c r="D25" s="45" t="s">
+      <c r="C21" s="11"/>
+      <c r="D21" s="26" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" s="8" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="45"/>
+      <c r="B26" s="46"/>
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+    </row>
+    <row r="27" spans="1:11" s="8" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="36"/>
+      <c r="B27" s="37"/>
+      <c r="C27" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="E25" s="47"/>
-    </row>
-    <row r="26" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="C26" s="12"/>
-      <c r="D26" s="31" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" s="8" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="58"/>
-      <c r="B31" s="59"/>
-      <c r="C31" s="59"/>
-      <c r="D31" s="59"/>
-      <c r="E31" s="60"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
-    </row>
-    <row r="32" spans="1:11" s="8" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="48"/>
-      <c r="B32" s="49"/>
-      <c r="C32" s="50" t="s">
-        <v>24</v>
-      </c>
-      <c r="D32" s="51"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-    </row>
-    <row r="33" spans="1:11" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="53"/>
-      <c r="B33" s="54"/>
-      <c r="C33" s="55" t="s">
-        <v>25</v>
-      </c>
-      <c r="D33" s="56"/>
-      <c r="E33" s="57"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+    </row>
+    <row r="28" spans="1:11" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="40"/>
+      <c r="B28" s="41"/>
+      <c r="C28" s="42" t="s">
+        <v>26</v>
+      </c>
+      <c r="D28" s="43"/>
+      <c r="E28" s="44"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="0.78749999999999998" bottom="0.95416666666666705" header="0.511811023622047" footer="0.78749999999999998"/>

--- a/template.xlsx
+++ b/template.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Khang\Documents\Github\Debt-Calculation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA64A381-7BFA-422D-BF98-A23386DAD4C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9C25106-2521-4498-8383-15DE3528CF0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="19440" windowHeight="10440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>BÁO CÁO THANH TOÁN CÔNG NỢ</t>
   </si>
@@ -44,18 +44,12 @@
     <t>MÃ BÁO CÁO:</t>
   </si>
   <si>
-    <t>yy_mm_dd_CUS-NAME.</t>
-  </si>
-  <si>
     <t>NGÀY RA BÁO CÁO</t>
   </si>
   <si>
     <t>LÃI SUẤT TÍNH:</t>
   </si>
   <si>
-    <t>3%/Tháng</t>
-  </si>
-  <si>
     <t>NGÀY CHỐT SỔ</t>
   </si>
   <si>
@@ -68,13 +62,7 @@
     <t>KHÁCH HÀNG:</t>
   </si>
   <si>
-    <t>Tên Khách Hàng Viết Hoa</t>
-  </si>
-  <si>
     <t>MÃ SỔ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,13,23, 1,23 ,12, 3,12 ,31 </t>
   </si>
   <si>
     <t>BẢNG TỔNG KẾT HÓA ĐƠN</t>
@@ -128,7 +116,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0\ [$₫-42A]_-;\-* #,##0\ [$₫-42A]_-;_-* &quot;-&quot;\ [$₫-42A]_-;_-@_-"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -230,12 +218,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <i/>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <b/>
       <u/>
       <sz val="18"/>
@@ -250,6 +232,17 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -384,202 +377,212 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -709,311 +712,327 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K28"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19" style="21" customWidth="1"/>
-    <col min="2" max="4" width="19" style="3" customWidth="1"/>
-    <col min="5" max="5" width="19" style="9" customWidth="1"/>
-    <col min="6" max="6" width="16" style="2" customWidth="1"/>
-    <col min="7" max="7" width="13.85546875" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="11.5703125" style="1"/>
+    <col min="1" max="4" width="19" style="9" customWidth="1"/>
+    <col min="5" max="5" width="19" style="79" customWidth="1"/>
+    <col min="6" max="6" width="16" style="5" customWidth="1"/>
+    <col min="7" max="7" width="13.85546875" style="5" customWidth="1"/>
+    <col min="8" max="11" width="11.5703125" style="6"/>
+    <col min="12" max="16384" width="11.5703125" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="58" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="28"/>
-    </row>
-    <row r="2" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="59" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" s="4" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="10"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="64" t="s">
+    <row r="1" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="4"/>
+    </row>
+    <row r="2" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="10"/>
+    </row>
+    <row r="3" spans="1:11" s="15" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="11"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-    </row>
-    <row r="4" spans="1:11" s="5" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="13" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+    </row>
+    <row r="4" spans="1:11" s="20" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="17"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="15" t="s">
+      <c r="E4" s="19"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+    </row>
+    <row r="5" spans="1:11" s="20" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="16"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-    </row>
-    <row r="5" spans="1:11" s="5" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="13" t="s">
+      <c r="B5" s="17"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="E5" s="21"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+    </row>
+    <row r="6" spans="1:11" s="20" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="12"/>
-      <c r="D5" s="15" t="s">
+      <c r="B6" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="17"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-    </row>
-    <row r="6" spans="1:11" s="5" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="13" t="s">
+      <c r="C6" s="14"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+    </row>
+    <row r="7" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B7" s="17"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-    </row>
-    <row r="7" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="13" t="s">
+      <c r="E7" s="24"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+    </row>
+    <row r="8" spans="1:11" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="25"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="10"/>
+    </row>
+    <row r="9" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" s="28"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="29"/>
+    </row>
+    <row r="11" spans="1:11" s="35" customFormat="1" ht="27" x14ac:dyDescent="0.25">
+      <c r="A11" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="12"/>
-      <c r="D7" s="15" t="s">
+      <c r="C11" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="D11" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D8" s="6"/>
-    </row>
-    <row r="9" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="74" t="s">
+      <c r="E11" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="27"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="28"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" s="22"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="17"/>
-    </row>
-    <row r="11" spans="1:11" s="49" customFormat="1" ht="27" x14ac:dyDescent="0.25">
-      <c r="A11" s="60" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="61" t="s">
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="34"/>
+      <c r="J11" s="34"/>
+      <c r="K11" s="34"/>
+    </row>
+    <row r="12" spans="1:11" s="20" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="36"/>
+      <c r="B12" s="37"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="39"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+    </row>
+    <row r="13" spans="1:11" s="20" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="40"/>
+      <c r="B13" s="41"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="43"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+    </row>
+    <row r="14" spans="1:11" s="20" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="40"/>
+      <c r="B14" s="41"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="43"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+    </row>
+    <row r="15" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="44"/>
+      <c r="B15" s="45"/>
+      <c r="C15" s="46"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+    </row>
+    <row r="16" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="62" t="s">
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="1:11" s="51" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="47"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="49"/>
+      <c r="E17" s="50"/>
+    </row>
+    <row r="18" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="52"/>
+      <c r="B18" s="53"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="55"/>
+      <c r="E18" s="56"/>
+    </row>
+    <row r="19" spans="1:11" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="57"/>
+      <c r="B19" s="53"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="58"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+    </row>
+    <row r="20" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="60"/>
+      <c r="B20" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="61" t="s">
+      <c r="C20" s="62"/>
+      <c r="D20" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="63" t="s">
+      <c r="E20" s="63"/>
+    </row>
+    <row r="21" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="25"/>
+      <c r="B21" s="64" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="48"/>
-      <c r="G11" s="48"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="48"/>
-      <c r="J11" s="48"/>
-      <c r="K11" s="48"/>
-    </row>
-    <row r="12" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="70"/>
-      <c r="B12" s="71"/>
-      <c r="C12" s="72"/>
-      <c r="D12" s="71"/>
-      <c r="E12" s="73"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-    </row>
-    <row r="13" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="23"/>
-      <c r="B13" s="29"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="31"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-    </row>
-    <row r="14" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="23"/>
-      <c r="B14" s="29"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="31"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-    </row>
-    <row r="15" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="25"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-    </row>
-    <row r="16" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="74" t="s">
+      <c r="C21" s="12"/>
+      <c r="D21" s="64" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" s="10"/>
+    </row>
+    <row r="22" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="25"/>
+      <c r="E22" s="10"/>
+    </row>
+    <row r="23" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="25"/>
+      <c r="E23" s="10"/>
+    </row>
+    <row r="24" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="25"/>
+      <c r="E24" s="10"/>
+    </row>
+    <row r="25" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="25"/>
+      <c r="E25" s="10"/>
+    </row>
+    <row r="26" spans="1:11" s="68" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="65"/>
+      <c r="B26" s="66"/>
+      <c r="C26" s="66"/>
+      <c r="D26" s="66"/>
+      <c r="E26" s="67"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+    </row>
+    <row r="27" spans="1:11" s="68" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="69"/>
+      <c r="B27" s="70"/>
+      <c r="C27" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="27"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="28"/>
-    </row>
-    <row r="17" spans="1:11" s="32" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="66"/>
-      <c r="B17" s="67"/>
-      <c r="C17" s="68"/>
-      <c r="D17" s="68"/>
-      <c r="E17" s="69"/>
-    </row>
-    <row r="18" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="65"/>
-      <c r="B18" s="51"/>
-      <c r="C18" s="52"/>
-      <c r="D18" s="53"/>
-      <c r="E18" s="54"/>
-    </row>
-    <row r="19" spans="1:11" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="56"/>
-      <c r="B19" s="51"/>
-      <c r="C19" s="52"/>
-      <c r="D19" s="50"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-    </row>
-    <row r="20" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="33"/>
-      <c r="B20" s="75" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" s="34"/>
-      <c r="D20" s="75" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="35"/>
-    </row>
-    <row r="21" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="11"/>
-      <c r="D21" s="26" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" s="8" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="45"/>
-      <c r="B26" s="46"/>
-      <c r="C26" s="46"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-    </row>
-    <row r="27" spans="1:11" s="8" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="36"/>
-      <c r="B27" s="37"/>
-      <c r="C27" s="57" t="s">
+      <c r="D27" s="72"/>
+      <c r="E27" s="73"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+    </row>
+    <row r="28" spans="1:11" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="74"/>
+      <c r="B28" s="75"/>
+      <c r="C28" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="38"/>
-      <c r="E27" s="39"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-    </row>
-    <row r="28" spans="1:11" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="40"/>
-      <c r="B28" s="41"/>
-      <c r="C28" s="42" t="s">
-        <v>26</v>
-      </c>
-      <c r="D28" s="43"/>
-      <c r="E28" s="44"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
+      <c r="D28" s="77"/>
+      <c r="E28" s="78"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="0.78749999999999998" bottom="0.95416666666666705" header="0.511811023622047" footer="0.78749999999999998"/>
-  <pageSetup paperSize="9" scale="91" fitToHeight="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="50" fitToHeight="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter differentFirst="1">
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;P/&amp;N</oddFooter>
     <firstFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;P/&amp;N</firstFooter>

--- a/template.xlsx
+++ b/template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Khang\Documents\Github\Debt-Calculation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9C25106-2521-4498-8383-15DE3528CF0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D80E83C-78A3-4DF9-A0C8-9596C69E0513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="19440" windowHeight="10440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -379,12 +379,6 @@
   </cellStyleXfs>
   <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
@@ -583,6 +577,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -718,314 +718,314 @@
   <dimension ref="A1:K28"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="4" width="19" style="9" customWidth="1"/>
-    <col min="5" max="5" width="19" style="79" customWidth="1"/>
-    <col min="6" max="6" width="16" style="5" customWidth="1"/>
-    <col min="7" max="7" width="13.85546875" style="5" customWidth="1"/>
-    <col min="8" max="11" width="11.5703125" style="6"/>
-    <col min="12" max="16384" width="11.5703125" style="7"/>
+    <col min="1" max="4" width="19" style="7" customWidth="1"/>
+    <col min="5" max="5" width="19" style="77" customWidth="1"/>
+    <col min="6" max="6" width="16" style="3" customWidth="1"/>
+    <col min="7" max="7" width="13.85546875" style="3" customWidth="1"/>
+    <col min="8" max="11" width="11.5703125" style="4"/>
+    <col min="12" max="16384" width="11.5703125" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="4"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="2"/>
     </row>
     <row r="2" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="10"/>
-    </row>
-    <row r="3" spans="1:11" s="15" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="11"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="13" t="s">
+      <c r="E2" s="8"/>
+    </row>
+    <row r="3" spans="1:11" s="13" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="9"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-    </row>
-    <row r="4" spans="1:11" s="20" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="16" t="s">
+      <c r="D3" s="12"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+    </row>
+    <row r="4" spans="1:11" s="18" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="18" t="s">
+      <c r="B4" s="15"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="19"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-    </row>
-    <row r="5" spans="1:11" s="20" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="16" t="s">
+      <c r="E4" s="17"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+    </row>
+    <row r="5" spans="1:11" s="18" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="17"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="18" t="s">
+      <c r="B5" s="15"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="21"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-    </row>
-    <row r="6" spans="1:11" s="20" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="16" t="s">
+      <c r="E5" s="19"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+    </row>
+    <row r="6" spans="1:11" s="18" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
     </row>
     <row r="7" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="18" t="s">
+      <c r="B7" s="15"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="24"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
+      <c r="E7" s="22"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
     </row>
     <row r="8" spans="1:11" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="25"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="10"/>
+      <c r="A8" s="23"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="8"/>
     </row>
     <row r="9" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="4"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" s="28"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="29"/>
-    </row>
-    <row r="11" spans="1:11" s="35" customFormat="1" ht="27" x14ac:dyDescent="0.25">
-      <c r="A11" s="30" t="s">
+      <c r="A10" s="26"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="27"/>
+    </row>
+    <row r="11" spans="1:11" s="33" customFormat="1" ht="27" x14ac:dyDescent="0.25">
+      <c r="A11" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="31" t="s">
+      <c r="B11" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="32" t="s">
+      <c r="C11" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="31" t="s">
+      <c r="D11" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="33" t="s">
+      <c r="E11" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="34"/>
-      <c r="I11" s="34"/>
-      <c r="J11" s="34"/>
-      <c r="K11" s="34"/>
-    </row>
-    <row r="12" spans="1:11" s="20" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="36"/>
-      <c r="B12" s="37"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="39"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-    </row>
-    <row r="13" spans="1:11" s="20" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="40"/>
-      <c r="B13" s="41"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="43"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-    </row>
-    <row r="14" spans="1:11" s="20" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="40"/>
-      <c r="B14" s="41"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="43"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="32"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="32"/>
+    </row>
+    <row r="12" spans="1:11" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="34"/>
+      <c r="B12" s="35"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="37"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+    </row>
+    <row r="13" spans="1:11" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="38"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="41"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+    </row>
+    <row r="14" spans="1:11" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="38"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="41"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
     </row>
     <row r="15" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="44"/>
-      <c r="B15" s="45"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
+      <c r="A15" s="42"/>
+      <c r="B15" s="43"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
     </row>
     <row r="16" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="27" t="s">
+      <c r="A16" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="4"/>
-    </row>
-    <row r="17" spans="1:11" s="51" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="47"/>
-      <c r="B17" s="48"/>
-      <c r="C17" s="49"/>
-      <c r="D17" s="49"/>
-      <c r="E17" s="50"/>
-    </row>
-    <row r="18" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="52"/>
-      <c r="B18" s="53"/>
-      <c r="C18" s="54"/>
-      <c r="D18" s="55"/>
-      <c r="E18" s="56"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="1:11" s="49" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="45"/>
+      <c r="B17" s="46"/>
+      <c r="C17" s="47"/>
+      <c r="D17" s="47"/>
+      <c r="E17" s="48"/>
+    </row>
+    <row r="18" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="50"/>
+      <c r="B18" s="51"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="54"/>
     </row>
     <row r="19" spans="1:11" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="57"/>
-      <c r="B19" s="53"/>
-      <c r="C19" s="54"/>
-      <c r="D19" s="58"/>
-      <c r="E19" s="59"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
+      <c r="A19" s="55"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
     </row>
     <row r="20" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="60"/>
-      <c r="B20" s="61" t="s">
+      <c r="A20" s="58"/>
+      <c r="B20" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="62"/>
-      <c r="D20" s="61" t="s">
+      <c r="C20" s="60"/>
+      <c r="D20" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="E20" s="63"/>
+      <c r="E20" s="61"/>
     </row>
     <row r="21" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="25"/>
-      <c r="B21" s="64" t="s">
+      <c r="A21" s="23"/>
+      <c r="B21" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="12"/>
-      <c r="D21" s="64" t="s">
+      <c r="C21" s="10"/>
+      <c r="D21" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="E21" s="10"/>
+      <c r="E21" s="8"/>
     </row>
     <row r="22" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="25"/>
-      <c r="E22" s="10"/>
+      <c r="A22" s="23"/>
+      <c r="E22" s="8"/>
     </row>
     <row r="23" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="25"/>
-      <c r="E23" s="10"/>
+      <c r="A23" s="23"/>
+      <c r="E23" s="8"/>
     </row>
     <row r="24" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="25"/>
-      <c r="E24" s="10"/>
+      <c r="A24" s="23"/>
+      <c r="E24" s="8"/>
     </row>
     <row r="25" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="25"/>
-      <c r="E25" s="10"/>
-    </row>
-    <row r="26" spans="1:11" s="68" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="65"/>
-      <c r="B26" s="66"/>
-      <c r="C26" s="66"/>
-      <c r="D26" s="66"/>
-      <c r="E26" s="67"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
-    </row>
-    <row r="27" spans="1:11" s="68" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="69"/>
-      <c r="B27" s="70"/>
-      <c r="C27" s="71" t="s">
+      <c r="A25" s="23"/>
+      <c r="E25" s="8"/>
+    </row>
+    <row r="26" spans="1:11" s="66" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="63"/>
+      <c r="B26" s="64"/>
+      <c r="C26" s="64"/>
+      <c r="D26" s="64"/>
+      <c r="E26" s="65"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+    </row>
+    <row r="27" spans="1:11" s="66" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="67"/>
+      <c r="B27" s="68"/>
+      <c r="C27" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="D27" s="72"/>
-      <c r="E27" s="73"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="71"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
     </row>
     <row r="28" spans="1:11" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="74"/>
-      <c r="B28" s="75"/>
-      <c r="C28" s="76" t="s">
+      <c r="A28" s="72"/>
+      <c r="B28" s="73"/>
+      <c r="C28" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="D28" s="77"/>
-      <c r="E28" s="78"/>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
+      <c r="D28" s="75"/>
+      <c r="E28" s="76"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
